--- a/events/Markkleeberg_2021_WC/Markkleeberg_2021_WC_start.xlsx
+++ b/events/Markkleeberg_2021_WC/Markkleeberg_2021_WC_start.xlsx
@@ -26146,6 +26146,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X444" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -34401,6 +34406,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X579" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -37481,6 +37491,11 @@
       <c r="R628" t="inlineStr">
         <is>
           <t>FISEROVA Tereza</t>
+        </is>
+      </c>
+      <c r="X628" t="inlineStr">
+        <is>
+          <t>42016</t>
         </is>
       </c>
     </row>
